--- a/assets/constructions/examples/ctd_mie_fe.xlsx
+++ b/assets/constructions/examples/ctd_mie_fe.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE6"/>
+  <dimension ref="A1:AI6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -584,39 +584,63 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>R216-25M25-089</t>
+          <t>RCF-C20-10R-160-2T</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SANDVIK</t>
+          <t>DEREK</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CoroMillⓇ 216 ball nose milling cutter</t>
+          <t>RCF</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E2" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="F2" t="inlineStr"/>
+        <v>20</v>
+      </c>
+      <c r="F2" t="n">
+        <v>160</v>
+      </c>
       <c r="G2" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="H2" t="n">
-        <v>88.90000000000001</v>
-      </c>
-      <c r="I2" t="inlineStr"/>
+        <v>18</v>
+      </c>
+      <c r="I2" t="n">
+        <v>60</v>
+      </c>
       <c r="J2" t="n">
-        <v>146.84</v>
+        <v>160</v>
       </c>
       <c r="K2" t="n">
         <v>2</v>
@@ -625,29 +649,27 @@
         <v>2</v>
       </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="n">
-        <v>24000</v>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
-        <v>0.446</v>
+        <v>0.3</v>
       </c>
       <c r="P2" t="n">
-        <v>12.5</v>
+        <v>18</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>CoroMill 216 (R216-2504)</t>
+          <t>ZCEW100CE/ZCEW100SE</t>
         </is>
       </c>
       <c r="R2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>HA</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -657,12 +679,12 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>HB-25.4</t>
+          <t>HA-20</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>COR_R216:25H</t>
+          <t>DER_ZCEW100H</t>
         </is>
       </c>
       <c r="Z2" t="n">
@@ -673,23 +695,41 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>SAND_R216-2504_H</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr"/>
+          <t>ZC..*E</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>DEREK</t>
+        </is>
+      </c>
       <c r="AD2" t="n">
         <v>0</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2021/www.sandvik.coromant.com</t>
-        </is>
+          <t>2019 / DEREK</t>
+        </is>
+      </c>
+      <c r="AF2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>106.85</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AI2" t="n">
+        <v>8758.91</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>RCF-C25-10R-200-2T</t>
+          <t>RCF-C32-15R-160-2T</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -703,43 +743,43 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E3" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F3" t="n">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="G3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H3" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="I3" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="J3" t="n">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="K3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
-        <v>0.65</v>
+        <v>0.8</v>
       </c>
       <c r="P3" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>ZCEW100CE/ZCEW100SE</t>
+          <t>ZCEW150CE/ZCEW150SE</t>
         </is>
       </c>
       <c r="R3" t="n">
@@ -760,12 +800,12 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>HA-25</t>
+          <t>HA-32</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>DER_ZCEW100H</t>
+          <t>DER_ZCEW150H</t>
         </is>
       </c>
       <c r="Z3" t="n">
@@ -791,44 +831,54 @@
         <is>
           <t>2019 / DEREK</t>
         </is>
+      </c>
+      <c r="AF3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>158.12</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AI3" t="n">
+        <v>12961.71</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>RCF-C32-12.5R-250-2T</t>
+          <t>R216-12A20-045</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DEREK</t>
+          <t>SANDVIK</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>RCF</t>
+          <t>CoroMillⓇ 216 ball nose milling cutter</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="E4" t="n">
-        <v>32</v>
-      </c>
-      <c r="F4" t="n">
-        <v>250</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
-        <v>12.5</v>
+        <v>6</v>
       </c>
       <c r="H4" t="n">
-        <v>23</v>
-      </c>
-      <c r="I4" t="n">
-        <v>90</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="K4" t="n">
         <v>2</v>
@@ -837,16 +887,18 @@
         <v>2</v>
       </c>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="N4" t="n">
+        <v>21000</v>
+      </c>
       <c r="O4" t="n">
-        <v>1.2</v>
+        <v>0.434</v>
       </c>
       <c r="P4" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>ZCEW125CE/ZCEW125SE</t>
+          <t>CoroMill 216 (R216-1202)</t>
         </is>
       </c>
       <c r="R4" t="n">
@@ -867,12 +919,12 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>HA-32</t>
+          <t>HA-20</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>DER_ZCEW125H</t>
+          <t>COR_R216:12H</t>
         </is>
       </c>
       <c r="Z4" t="n">
@@ -883,57 +935,61 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>ZC..*E</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>DEREK</t>
-        </is>
-      </c>
+          <t>SAND_R216-1202_H</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="n">
         <v>0</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2019 / DEREK</t>
-        </is>
-      </c>
+          <t>2021/www.sandvik.coromant.com</t>
+        </is>
+      </c>
+      <c r="AF4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BCM D12-B-C16</t>
+          <t>RCF-C32-12.5R-250-2T</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ISCAR</t>
+          <t>DEREK</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DROP MILL</t>
+          <t>RCF</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="E5" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="F5" t="n">
-        <v>160</v>
+        <v>250</v>
       </c>
       <c r="G5" t="n">
-        <v>6</v>
-      </c>
-      <c r="H5" t="inlineStr"/>
+        <v>12.5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>23</v>
+      </c>
       <c r="I5" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="J5" t="n">
-        <v>160</v>
+        <v>250</v>
       </c>
       <c r="K5" t="n">
         <v>2</v>
@@ -944,14 +1000,14 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
-        <v>0.22</v>
+        <v>1.2</v>
       </c>
       <c r="P5" t="n">
-        <v>11.4</v>
+        <v>23</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>BCR D120-QT</t>
+          <t>ZCEW125CE/ZCEW125SE</t>
         </is>
       </c>
       <c r="R5" t="n">
@@ -966,20 +1022,18 @@
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
-      <c r="V5" t="n">
-        <v>2</v>
-      </c>
+      <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
         <v>1</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>HA-16</t>
+          <t>HA-32</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>ISCAR_BCR_D120</t>
+          <t>DER_ZCEW125H</t>
         </is>
       </c>
       <c r="Z5" t="n">
@@ -990,12 +1044,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>ISC_BCR_D120</t>
+          <t>ZC..*E</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>ISCAR</t>
+          <t>DEREK</t>
         </is>
       </c>
       <c r="AD5" t="n">
@@ -1003,75 +1057,87 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2020 / Iscar главный каталог</t>
-        </is>
+          <t>2019 / DEREK</t>
+        </is>
+      </c>
+      <c r="AF5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>160.26</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AI5" t="n">
+        <v>13137.14</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>RCFL-C20-10R-200-4T</t>
+          <t>R216-40B40-100</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DEREK</t>
+          <t>SANDVIK</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>RCFL</t>
+          <t>CoroMillⓇ 216 ball nose milling cutter</t>
         </is>
       </c>
       <c r="D6" t="n">
+        <v>40</v>
+      </c>
+      <c r="E6" t="n">
+        <v>40</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="n">
         <v>20</v>
       </c>
-      <c r="E6" t="n">
+      <c r="H6" t="n">
+        <v>100</v>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="n">
+        <v>171</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2</v>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="n">
+        <v>8000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.321</v>
+      </c>
+      <c r="P6" t="n">
         <v>20</v>
       </c>
-      <c r="F6" t="n">
-        <v>200</v>
-      </c>
-      <c r="G6" t="n">
-        <v>10</v>
-      </c>
-      <c r="H6" t="n">
-        <v>24</v>
-      </c>
-      <c r="I6" t="n">
-        <v>70</v>
-      </c>
-      <c r="J6" t="n">
-        <v>200</v>
-      </c>
-      <c r="K6" t="n">
-        <v>4</v>
-      </c>
-      <c r="L6" t="n">
-        <v>4</v>
-      </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="P6" t="n">
-        <v>24</v>
-      </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>ZCEW100CE/ZCEW100SE/SPMT080204</t>
+          <t>CoroMill 216 (APMT160408-M) | CoroMill 216 (R216-4007)</t>
         </is>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>HA</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1081,38 +1147,40 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>HA-20</t>
+          <t>HB-40</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>DER_ZCEW100H+DER_SPMT0802H</t>
+          <t>COR_AP1604H+COR_R216-4007H</t>
         </is>
       </c>
       <c r="Z6" t="n">
         <v>1</v>
       </c>
       <c r="AA6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>ZC..*E</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>DEREK</t>
-        </is>
-      </c>
+          <t>SAND_APMT1604 | R216-4007_H</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="n">
         <v>0</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>2019 / DEREK</t>
-        </is>
-      </c>
+          <t>2021/www.sandvik.coromant.com</t>
+        </is>
+      </c>
+      <c r="AF6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
